--- a/evaluation_forms/045_wine_tasting_evaluation_form--evaluation_forms.xlsx
+++ b/evaluation_forms/045_wine_tasting_evaluation_form--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'red',_'label':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Red', 'label': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'white',_'label':_'white'}</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'White', 'label': 'White'}</t>
+          <t>White</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'sparkling',_'label':_'sparkling'}</t>
+          <t>sparkling</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Sparkling', 'label': 'Sparkling'}</t>
+          <t>Sparkling</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'bordeaux',_'label':_'bordeaux'}</t>
+          <t>bordeaux</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Bordeaux', 'label': 'Bordeaux'}</t>
+          <t>Bordeaux</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'burgundy',_'label':_'burgundy'}</t>
+          <t>burgundy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Burgundy', 'label': 'Burgundy'}</t>
+          <t>Burgundy</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'rioja',_'label':_'rioja'}</t>
+          <t>rioja</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Rioja', 'label': 'Rioja'}</t>
+          <t>Rioja</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_1990,_'label':_1990}</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 1990, 'label': 1990}</t>
+          <t>1990</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_1995,_'label':_1995}</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 1995, 'label': 1995}</t>
+          <t>1995</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_2000,_'label':_2000}</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 2000, 'label': 2000}</t>
+          <t>2000</t>
         </is>
       </c>
     </row>
